--- a/hira_material_automation/output/monthly/202601_202609__acl_interference_screw_absorbable__040012__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202609__acl_interference_screw_absorbable__040012__normalized.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-04T22:54:21</t>
+          <t>2026-09-14T23:45:52</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6dbf1a4555a6589ccc0bacdb87b99077be0d43997ed190ed6c7c9193db8d3b5d</t>
+          <t>31e228ac1d215ba212c057f4751886ad6d97b86df9aeebf72c573f47102fdca6</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202609__acl_interference_screw_absorbable__040012__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202609__acl_interference_screw_absorbable__040012__normalized.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-14T23:45:52</t>
+          <t>2026-09-24T23:49:17</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31e228ac1d215ba212c057f4751886ad6d97b86df9aeebf72c573f47102fdca6</t>
+          <t>cdcca554dc23f3d76b8349236b7af37535f6cc4c8f315af09c5c68d1026aed91</t>
         </is>
       </c>
     </row>
